--- a/artfynd/A 51447-2024 artfynd.xlsx
+++ b/artfynd/A 51447-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328614</v>
+        <v>124328587</v>
       </c>
       <c r="B2" t="n">
-        <v>91700</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518560</v>
+        <v>518553</v>
       </c>
       <c r="R2" t="n">
-        <v>6339244</v>
+        <v>6339274</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,39 +779,23 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även en del spillning och betade tallar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Granhögstubbe.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328587</v>
+        <v>124328614</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>91700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,21 +829,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -862,17 +851,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518553</v>
+        <v>518560</v>
       </c>
       <c r="R3" t="n">
-        <v>6339274</v>
+        <v>6339244</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -928,23 +912,39 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även en del spillning och betade tallar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 51447-2024 artfynd.xlsx
+++ b/artfynd/A 51447-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328587</v>
+        <v>124328614</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>91700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,17 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518553</v>
+        <v>518560</v>
       </c>
       <c r="R2" t="n">
-        <v>6339274</v>
+        <v>6339244</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -779,23 +774,39 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Även en del spillning och betade tallar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328614</v>
+        <v>124328587</v>
       </c>
       <c r="B3" t="n">
-        <v>91700</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,21 +840,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -851,12 +862,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -864,10 +880,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518560</v>
+        <v>518553</v>
       </c>
       <c r="R3" t="n">
-        <v>6339244</v>
+        <v>6339274</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -912,39 +928,23 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även en del spillning och betade tallar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granhögstubbe.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 51447-2024 artfynd.xlsx
+++ b/artfynd/A 51447-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>124328614</v>
       </c>
       <c r="B2" t="n">
-        <v>91700</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,12 +822,7 @@
         <v>124328587</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
